--- a/DeepLearningTopics.xlsx
+++ b/DeepLearningTopics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\TechManagement\Deeplearning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C73F93C-493B-4AC2-B9DA-587B7100EDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58983792-6FFE-45A1-9196-7EA76CDEDB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{195D9DE4-3149-447D-8697-146045E90AD9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Topic</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>https://github.com/Balachandar-Ganesan/DeepLearning/blob/main/200_6_HowtoUseOpenSourceLLM.ipynb</t>
+  </si>
+  <si>
+    <t>NLP Correcting Language Translation Demo</t>
+  </si>
+  <si>
+    <t>https://github.com/Balachandar-Ganesan/DeepLearning/blob/main/NLPLanguageTranslation.ipynb</t>
   </si>
 </sst>
 </file>
@@ -571,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C6711AB-3C36-4053-8286-FF41D8EEA6B2}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="64.08984375" style="1" customWidth="1"/>
@@ -790,6 +796,14 @@
       </c>
       <c r="B29" s="2" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
